--- a/dashboard/backend/src/data/candidates.xlsx
+++ b/dashboard/backend/src/data/candidates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahes\Desktop\technologia_round2\round_2\dashboard\backend\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E344586F-C63B-47E5-BFFC-C631087C2907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D6E0BB-8312-4CA9-BC10-94135FBB6A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>score</t>
   </si>
   <si>
-    <t>Aarav Sharma</t>
-  </si>
-  <si>
     <t>aarav.sharma@example.com</t>
   </si>
   <si>
@@ -92,6 +89,9 @@
   </si>
   <si>
     <t>tn105</t>
+  </si>
+  <si>
+    <t>Aarav Mishra</t>
   </si>
 </sst>
 </file>
@@ -375,16 +375,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E2" s="1">
         <v>88</v>
@@ -392,16 +392,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="E3" s="1">
         <v>92</v>
@@ -409,16 +409,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E4" s="1">
         <v>76</v>
@@ -426,16 +426,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
         <v>95</v>
@@ -443,16 +443,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E6" s="1">
         <v>81</v>

--- a/dashboard/backend/src/data/candidates.xlsx
+++ b/dashboard/backend/src/data/candidates.xlsx
@@ -1,120 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahes\Desktop\technologia_round2\round_2\dashboard\backend\src\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D6E0BB-8312-4CA9-BC10-94135FBB6A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name=" srcscriptsseedCandidates.js_x000a_im" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" srcscriptsseedCandidates.js_x000a_im" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>branch</t>
-  </si>
-  <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>aarav.sharma@example.com</t>
-  </si>
-  <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
-    <t>Priya Patel</t>
-  </si>
-  <si>
-    <t>priya.patel@example.com</t>
-  </si>
-  <si>
-    <t>Information Technology</t>
-  </si>
-  <si>
-    <t>Rohan Verma</t>
-  </si>
-  <si>
-    <t>rohan.verma@example.com</t>
-  </si>
-  <si>
-    <t>Electronics</t>
-  </si>
-  <si>
-    <t>Ananya Iyer</t>
-  </si>
-  <si>
-    <t>ananya.iyer@example.com</t>
-  </si>
-  <si>
-    <t>Vikram Singh</t>
-  </si>
-  <si>
-    <t>vikram.singh@example.com</t>
-  </si>
-  <si>
-    <t>Mechanical</t>
-  </si>
-  <si>
-    <t>tn101</t>
-  </si>
-  <si>
-    <t>tn102</t>
-  </si>
-  <si>
-    <t>tn103</t>
-  </si>
-  <si>
-    <t>tn104</t>
-  </si>
-  <si>
-    <t>tn105</t>
-  </si>
-  <si>
-    <t>Aarav Mishra</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -133,22 +51,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -349,113 +326,414 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.7" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>tn101</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Aarav Mishra</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>aarav.sharma@example.com</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>tn102</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>priya.patel@example.com</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>tn103</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Rohan Verma</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>rohan.verma@example.com</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>tn104</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ananya.iyer@example.com</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tn105</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>vikram.singh@example.com</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TN101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Candidate 101</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>candidate101@example.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AIML</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TN102</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Candidate 102</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>candidate102@example.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AIML</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TN103</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Candidate 103</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>candidate103@example.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TN104</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Candidate 104</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>candidate104@example.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TN105</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Candidate 105</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>candidate105@example.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TN106</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Candidate 106</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>candidate106@example.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TN107</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Candidate 107</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>candidate107@example.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TN108</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Candidate 108</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>candidate108@example.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TN109</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Candidate 109</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>candidate109@example.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ECE</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TN110</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Candidate 110</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>candidate110@example.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
